--- a/(붙임2) AI활용대체시장정보_신청양식_부서명.xlsx
+++ b/(붙임2) AI활용대체시장정보_신청양식_부서명.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ki/Documents/KOTRA_Report_Auto/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FEFF345-66C1-451A-81BF-3E71F4EBB34B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD0D4E00-9AC8-9042-89AE-5F55C404514A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31860" yWindow="1275" windowWidth="25755" windowHeight="14535" xr2:uid="{B46CDF17-D3C1-4690-97F2-2CDBAC0D0B10}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17740" xr2:uid="{B46CDF17-D3C1-4690-97F2-2CDBAC0D0B10}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,9 +32,6 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -573,7 +570,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
   <si>
     <t>국내기업명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -678,13 +675,20 @@
   <si>
     <t>-</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>튀르키에</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초보기업 ($1~$99,999)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1146,21 +1150,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{411ACBC5-F39F-43D4-B2D8-3F3BEB461FFF}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="2" max="2" width="14.5" customWidth="1"/>
-    <col min="3" max="3" width="11.125" customWidth="1"/>
-    <col min="4" max="4" width="14.75" customWidth="1"/>
-    <col min="5" max="5" width="19.125" customWidth="1"/>
-    <col min="6" max="6" width="15.875" customWidth="1"/>
-    <col min="7" max="7" width="13.25" customWidth="1"/>
-    <col min="8" max="8" width="27.375" customWidth="1"/>
-    <col min="9" max="9" width="16.25" customWidth="1"/>
-    <col min="10" max="10" width="22.75" customWidth="1"/>
-    <col min="11" max="11" width="20.125" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" customWidth="1"/>
+    <col min="5" max="5" width="19.1640625" customWidth="1"/>
+    <col min="6" max="6" width="15.83203125" customWidth="1"/>
+    <col min="7" max="7" width="13.1640625" customWidth="1"/>
+    <col min="8" max="8" width="27.33203125" customWidth="1"/>
+    <col min="9" max="9" width="16.1640625" customWidth="1"/>
+    <col min="10" max="10" width="22.6640625" customWidth="1"/>
+    <col min="11" max="11" width="20.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="27" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="32">
       <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
@@ -1195,7 +1199,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -1228,22 +1232,32 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="F3" s="3">
+        <v>330499</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="J3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="1"/>
+      <c r="K3" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1258,7 +1272,7 @@
       </c>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1271,7 +1285,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1287,6 +1301,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
@@ -1312,12 +1327,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F71A326-013D-4047-BAB1-4E80C4E51BBA}">
   <dimension ref="B2:G6"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
-    <col min="7" max="7" width="13.375" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:7">
       <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
@@ -1325,7 +1340,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:7">
       <c r="B3" s="5" t="s">
         <v>12</v>
       </c>
@@ -1333,17 +1348,17 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:7">
       <c r="B4" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:7">
       <c r="B5" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:7">
       <c r="B6" s="5" t="s">
         <v>16</v>
       </c>
